--- a/frontend/src/assets/Template.xlsx
+++ b/frontend/src/assets/Template.xlsx
@@ -76,14 +76,14 @@
     <comment ref="BS2" authorId="0">
       <text>
         <r>
-          <t>Only when Funding Source = "Central - State Share".</t>
+          <t>Only when Funding Source = "Central - State Share". Central % + State % must not exceed 100.</t>
         </r>
       </text>
     </comment>
     <comment ref="BT2" authorId="0">
       <text>
         <r>
-          <t>Only when Funding Source = "Central - State Share".</t>
+          <t>Only when Funding Source = "Central - State Share". Central % + State % must not exceed 100.</t>
         </r>
       </text>
     </comment>
@@ -145,7 +145,7 @@
     <t>CoS/EoT events, GeoTagging photos, and Management Action items each belong to a project but are entered from the Input Sheet directly after the project exists — the "…Log" sheets here are blank reference templates for jotting that data down by hand, not something this import reads.</t>
   </si>
   <si>
-    <t>Generated: 2026-09-01 14:28:17Z</t>
+    <t>Generated: 2026-09-02 11:46:57Z</t>
   </si>
   <si>
     <t>#</t>
@@ -382,10 +382,10 @@
     <t>Expenditure Incurred (Rs. Cr.)</t>
   </si>
   <si>
-    <t>Central Share (Rs. Cr.)</t>
-  </si>
-  <si>
-    <t>State Share (Rs. Cr.)</t>
+    <t>Central Share (%)</t>
+  </si>
+  <si>
+    <t>State Share (%)</t>
   </si>
   <si>
     <t>Text</t>
@@ -1472,7 +1472,7 @@
     <col min="67" max="67" width="26" customWidth="1"/>
     <col min="68" max="69" width="20" customWidth="1"/>
     <col min="70" max="70" width="22" customWidth="1"/>
-    <col min="71" max="72" width="20" customWidth="1"/>
+    <col min="71" max="72" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
@@ -2120,10 +2120,10 @@
         <v>105</v>
       </c>
       <c r="BS3" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="BT3" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -3210,11 +3210,13 @@
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BR4:BR203">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BS4:BS203">
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="Invalid percentage" error="Enter a number between 0 and 100 (e.g. 42.5, not 0.425)." sqref="BS4:BS203">
       <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a non-negative number (e.g. 12.5)." sqref="BT4:BT203">
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="Invalid percentage" error="Enter a number between 0 and 100 (e.g. 42.5, not 0.425)." sqref="BT4:BT203">
       <formula1>0</formula1>
+      <formula2>100</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Pick a name from the Sectors sheet." sqref="C4:C203">
       <formula1>=Sectors!$A$2:$A$6</formula1>
